--- a/ForHome8/DataScience/model_report_task04.xlsx
+++ b/ForHome8/DataScience/model_report_task04.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="29">
   <si>
     <t xml:space="preserve">Model</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t xml:space="preserve">{'agglomerative__linkage': 'single', 'agglomerative__distance_threshold': np.float64(4.9)}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is the best model, because it has the highest silhouette metric. The companies that are colored in orange tend to change in the same way. Other than Google Alphabet, Apple, MasterCard, Amazon and Goldman Sachs - the other companies follow similar trends.</t>
   </si>
   <si>
     <t xml:space="preserve">{'agglomerative__linkage': 'single', 'agglomerative__distance_threshold': np.float64(4.800000000000001)}</t>
@@ -138,12 +141,18 @@
       <family val="0"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77BC65"/>
+        <bgColor rgb="FF99CC00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -180,8 +189,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -194,6 +215,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF77BC65"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -208,9 +289,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -223,8 +304,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="38979360" y="190440"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="38977560" y="190440"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -245,9 +326,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -260,8 +341,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="38979360" y="6534000"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="38977560" y="6534000"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -282,9 +363,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -297,8 +378,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="46035720" y="6534000"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="46033560" y="6534000"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -319,9 +400,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -334,8 +415,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="38979360" y="12877920"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="38977560" y="12877920"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -356,9 +437,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -371,8 +452,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="46035720" y="12877920"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="46033560" y="12877920"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -393,9 +474,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -408,8 +489,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="38979360" y="19221480"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="38977560" y="19221480"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -430,9 +511,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -445,8 +526,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="46035720" y="19221480"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="46033560" y="19221480"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -467,9 +548,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -482,8 +563,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="38979360" y="25565040"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="38977560" y="25565040"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -504,9 +585,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -519,8 +600,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="46035720" y="25565040"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="46033560" y="25565040"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -541,9 +622,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -556,8 +637,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="38979360" y="31908600"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="38977560" y="31908600"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -578,9 +659,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -593,8 +674,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="46035720" y="31908600"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="46033560" y="31908600"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -615,9 +696,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -630,8 +711,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="38979360" y="38252520"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="38977560" y="38252520"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -652,9 +733,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -667,8 +748,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="46035720" y="38252520"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="46033560" y="38252520"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -689,9 +770,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -704,8 +785,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="38979360" y="44596080"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="38977560" y="44596080"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -726,9 +807,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -741,8 +822,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="46035720" y="44596080"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="46033560" y="44596080"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -763,9 +844,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -778,8 +859,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="38979360" y="50939640"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="38977560" y="50939640"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -800,9 +881,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -815,8 +896,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="46035720" y="50939640"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="46033560" y="50939640"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -837,9 +918,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -852,8 +933,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="38979360" y="57283200"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="38977560" y="57283200"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -874,9 +955,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -889,8 +970,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="46035720" y="57283200"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="46033560" y="57283200"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -911,9 +992,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -926,8 +1007,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="38979360" y="63627120"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="38977560" y="63627120"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -948,9 +1029,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -963,8 +1044,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="46035720" y="63627120"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="46033560" y="63627120"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -985,9 +1066,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1000,8 +1081,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="38979360" y="69970680"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="38977560" y="69970680"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1022,9 +1103,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1037,8 +1118,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="46035720" y="69970680"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="46033560" y="69970680"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1059,9 +1140,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1074,8 +1155,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="38979360" y="76314240"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="38977560" y="76314240"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1096,9 +1177,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1111,8 +1192,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="46035720" y="76314240"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="46033560" y="76314240"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1133,9 +1214,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1148,8 +1229,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="38979360" y="82657800"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="38977560" y="82657800"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1170,9 +1251,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1185,8 +1266,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="46035720" y="82657800"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="46033560" y="82657800"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1207,9 +1288,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1222,8 +1303,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="38979360" y="89001720"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="38977560" y="89001720"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1244,9 +1325,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1259,8 +1340,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="46035720" y="89001720"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="46033560" y="89001720"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1281,9 +1362,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1296,8 +1377,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="38979360" y="95345280"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="38977560" y="95345280"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1318,9 +1399,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1333,8 +1414,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="46035720" y="95345280"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="46033560" y="95345280"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1355,9 +1436,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1370,8 +1451,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="38979360" y="101688840"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="38977560" y="101688840"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1392,9 +1473,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1407,8 +1488,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="46035720" y="101688840"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="46033560" y="101688840"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1429,9 +1510,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1444,8 +1525,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="38979360" y="108032400"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="38977560" y="108032400"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1466,9 +1547,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1481,8 +1562,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="46035720" y="108032400"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="46033560" y="108032400"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1503,9 +1584,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1518,8 +1599,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="38979360" y="114376320"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="38977560" y="114376320"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1540,9 +1621,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1555,8 +1636,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="46035720" y="114376320"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="46033560" y="114376320"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1577,9 +1658,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1592,8 +1673,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="38979360" y="120719880"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="38977560" y="120719880"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1614,9 +1695,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1629,8 +1710,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="46035720" y="120719880"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="46033560" y="120719880"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1651,9 +1732,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1666,8 +1747,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="38979360" y="127063440"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="38977560" y="127063440"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1688,9 +1769,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1703,8 +1784,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="46035720" y="127063440"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="46033560" y="127063440"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1725,7 +1806,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1743,19 +1824,20 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N22"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="295.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="29.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="29.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="95.08"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="33.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="29.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="100"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="142.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="142.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="10.99"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1816,27 +1898,34 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="499.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" s="3" customFormat="true" ht="499.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>963</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1" t="n">
         <v>0.0114372431700532</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3" s="1" t="n">
         <v>-101.143724317005</v>
       </c>
-      <c r="I3" s="0" t="n">
+      <c r="H3" s="1"/>
+      <c r="I3" s="1" t="n">
         <v>0</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="499.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1850,7 +1939,7 @@
         <v>963</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>0.0114372431700532</v>
@@ -1873,7 +1962,7 @@
         <v>963</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>0.00654345580458287</v>
@@ -1896,7 +1985,7 @@
         <v>963</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>0.0114372431700532</v>
@@ -1919,7 +2008,7 @@
         <v>963</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>0.00654345580458287</v>
@@ -1942,7 +2031,7 @@
         <v>963</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F8" s="0" t="n">
         <v>0.00654345580458287</v>
@@ -1965,7 +2054,7 @@
         <v>963</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9" s="0" t="n">
         <v>0.00654345580458287</v>
@@ -1988,7 +2077,7 @@
         <v>963</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F10" s="0" t="n">
         <v>0.00654345580458287</v>
@@ -2011,7 +2100,7 @@
         <v>963</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F11" s="0" t="n">
         <v>0.00654345580458287</v>
@@ -2034,7 +2123,7 @@
         <v>963</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F12" s="0" t="n">
         <v>0.00654345580458287</v>
@@ -2051,13 +2140,13 @@
         <v>15</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" s="0" t="n">
         <v>963</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F13" s="0" t="n">
         <v>0.0114372431700532</v>
@@ -2074,13 +2163,13 @@
         <v>15</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" s="0" t="n">
         <v>963</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F14" s="0" t="n">
         <v>0.0114372431700532</v>
@@ -2097,13 +2186,13 @@
         <v>15</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C15" s="0" t="n">
         <v>963</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F15" s="0" t="n">
         <v>0.0114372431700532</v>
@@ -2120,13 +2209,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C16" s="0" t="n">
         <v>963</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F16" s="0" t="n">
         <v>0.0114372431700532</v>
@@ -2143,13 +2232,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" s="0" t="n">
         <v>963</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F17" s="0" t="n">
         <v>0.0114372431700532</v>
@@ -2166,13 +2255,13 @@
         <v>15</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="0" t="n">
         <v>963</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F18" s="0" t="n">
         <v>0.00654345580458287</v>
@@ -2189,13 +2278,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" s="0" t="n">
         <v>963</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F19" s="0" t="n">
         <v>0.0114372431700532</v>
@@ -2212,13 +2301,13 @@
         <v>15</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C20" s="0" t="n">
         <v>963</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F20" s="0" t="n">
         <v>0.0114372431700532</v>
@@ -2235,7 +2324,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C21" s="0" t="n">
         <v>963</v>
@@ -2258,13 +2347,13 @@
         <v>15</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C22" s="0" t="n">
         <v>963</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F22" s="0" t="n">
         <v>0.0114372431700532</v>
